--- a/SauceDemo-Manual-Testing/Test-Cases/SauceDemo_TestCases.xlsx
+++ b/SauceDemo-Manual-Testing/Test-Cases/SauceDemo_TestCases.xlsx
@@ -5,19 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Documents\QA-Portfolio\SauceDemo-Manual-Testing\Bug-Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\OneDrive\Documents\QA-Portfolio\SauceDemo-Manual-Testing\Test-Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAB760F-579B-4F46-833E-3CA9098A1147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7614554-C9BE-4320-8911-835CCFC3BA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{C1EB83E1-F0DA-4A5E-ACF8-7F506BDE5434}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{C1EB83E1-F0DA-4A5E-ACF8-7F506BDE5434}"/>
   </bookViews>
   <sheets>
     <sheet name="Login TestCases" sheetId="1" r:id="rId1"/>
     <sheet name="Product TestCases" sheetId="3" r:id="rId2"/>
     <sheet name="Cart TestCases" sheetId="4" r:id="rId3"/>
     <sheet name="Checkout TestCases" sheetId="5" r:id="rId4"/>
-    <sheet name="SauceDemo Bugsheet" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5676,14 +5675,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D9F180-BDBC-45CB-93FF-196F01780887}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>